--- a/Outputs/PtX_demand_RO.xlsx
+++ b/Outputs/PtX_demand_RO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,62 +488,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2030</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0005636930456788687</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>0.0007755803143845905</v>
-      </c>
+        <v>0.003347484038416777</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.01083623726744989</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.003837294723497144</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>1.5099343443556e-09</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.0004504922364282554</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2030</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>0.0005636930456788687</v>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.0007755803143845905</v>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>1.5099343443556e-09</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0004504922364282554</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2030</v>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
-        <v>0.01071868213731395</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -555,14 +559,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2030</v>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>0.01071868213731395</v>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -574,7 +580,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -582,24 +588,18 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>0.001321923751049473</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.0002946819053396</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>6.918841025270784e-05</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -607,14 +607,16 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.001321923751049473</v>
+      </c>
       <c r="F7" t="n">
-        <v>0.0029881629419515</v>
+        <v>0.0002946819053396</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.0003155790193653426</v>
+        <v>6.918841025270784e-05</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -622,7 +624,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -631,17 +633,21 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.0029881629419515</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0.0003155790193653426</v>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -650,29 +656,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0.01480344166157238</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.0001343076135147</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.003749381908909639</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0150833559148795</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.0002528386855318</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.0051948817831295</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -682,28 +676,28 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.1394516376886295</v>
+        <v>0.01480344166157238</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0009458891369323</v>
+        <v>0.0001343076135147</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0341995366953689</v>
+        <v>0.003749381908909639</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09419884985513931</v>
+        <v>0.0150833559148795</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0015304330954511</v>
+        <v>0.0002528386855318</v>
       </c>
       <c r="K10" t="n">
-        <v>0.04768466602398019</v>
+        <v>0.0051948817831295</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -711,20 +705,30 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>0.003278749924607429</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.1394516376886295</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0009458891369323</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0341995366953689</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.09419884985513931</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0015304330954511</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.04768466602398019</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -733,7 +737,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.001418135584532027</v>
+        <v>0.003278749924607429</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -745,100 +749,102 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2030</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0005636930456788687</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.01071868213731395</v>
-      </c>
+        <v>0.005073237411109819</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.006018809260188929</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.1583135045118776</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.001080196750447</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.03794892011421288</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.1101174654360651</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.0017832717809829</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.05287954780710969</v>
-      </c>
+        <v>0.02466053402023349</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2040</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.001614804446179017</v>
-      </c>
+        <v>2030</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>0.0036905536638659</v>
-      </c>
+      <c r="E14" t="n">
+        <v>0.001418135584532027</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>1.263981819647457e-07</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.0006354295664757</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+        <v>2030</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.008984414495205465</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.02155491940476384</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.03451663800391957</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1583135045118776</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.001080196750447</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.03794892011421288</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1101174654360651</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.0017832717809829</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.05287954780710969</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2040</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>0.002622470521128136</v>
+      </c>
       <c r="D16" t="n">
-        <v>0.008216655125306753</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
+        <v>0.01065351620247373</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.003967993178665898</v>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -849,22 +855,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2040</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>0.001614804446179017</v>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>1.411418525020487e-09</v>
+        <v>0.0036905536638659</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>1.263981819647457e-07</v>
+      </c>
       <c r="I17" t="n">
-        <v>1.891418767955749e-10</v>
+        <v>0.0006354295664757</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -872,7 +882,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -880,47 +890,39 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
-        <v>0.005249890622688761</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.0003473543858705</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>0.0001299934446870049</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2040</v>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>0.008216655125306753</v>
+      </c>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>0.0016676381462925</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>0.0003320554996693197</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -929,17 +931,21 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>1.411418525020487e-09</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>1.891418767955749e-10</v>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -947,30 +953,24 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>0.005249890622688761</v>
+      </c>
       <c r="F21" t="n">
-        <v>0.006877661779708368</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.0002189435674046</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.0045867319142269</v>
-      </c>
+        <v>0.0003473543858705</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.0098279020055335</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.0003071579676164</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.0060974512509034</v>
-      </c>
+        <v>0.0001299934446870049</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -980,28 +980,20 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.039865990417804</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.0010168834109446</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.0322537194880227</v>
-      </c>
+        <v>0.0016676381462925</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.0414804807529571</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.0013581224519344</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.0455016934531268</v>
-      </c>
+        <v>0.0003320554996693197</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1009,9 +1001,7 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>0.003322654056724997</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1022,7 +1012,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1030,92 +1020,94 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>0.005671361021945911</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.006877661779708368</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0002189435674046</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0045867319142269</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0098279020055335</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0003071579676164</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.0060974512509034</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2040</v>
       </c>
-      <c r="C25" t="n">
-        <v>0.001614804446179017</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.008216655125306753</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.01424390570135967</v>
-      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0.05244919980495979</v>
+        <v>0.039865990417804</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0012358269783492</v>
+        <v>0.0010168834109446</v>
       </c>
       <c r="H25" t="n">
-        <v>0.03684057780043156</v>
+        <v>0.0322537194880227</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0524058614584645</v>
+        <v>0.0414804807529571</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0016652804195508</v>
+        <v>0.0013581224519344</v>
       </c>
       <c r="K25" t="n">
-        <v>0.05159914470403019</v>
+        <v>0.0455016934531268</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.00338334520507663</v>
-      </c>
+        <v>2040</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>0.005136423638254999</v>
-      </c>
+      <c r="E26" t="n">
+        <v>0.003322654056724997</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>2.142347372596333e-07</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.0010083991066546</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
+        <v>2040</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.002422206669268525</v>
+      </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>0.01638187746695201</v>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1126,17 +1118,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="n">
-        <v>0.007194422490000695</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0.005671361021945911</v>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1147,70 +1139,88 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+        <v>2040</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.006659481636575678</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.01887017132778048</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.03459377634697757</v>
+      </c>
       <c r="F29" t="n">
-        <v>1.83608376887917e-08</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+        <v>0.05244919980495979</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0012358269783492</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.03684057780043156</v>
+      </c>
       <c r="I29" t="n">
-        <v>4.084482658611099e-09</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+        <v>0.0524058614584645</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.0016652804195508</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.05159914470403019</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2050</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>0.002326257700541548</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.01057886335704874</v>
+      </c>
       <c r="E30" t="n">
-        <v>0.01308643669280649</v>
-      </c>
-      <c r="F30" t="n">
-        <v>6.640844061930469e-05</v>
-      </c>
+        <v>0.004021391573493941</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>3.813628671025667e-05</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>2050</v>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="n">
+        <v>0.00338334520507663</v>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>0.000131868484186315</v>
+        <v>0.005136423638254999</v>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>2.142347372596333e-07</v>
+      </c>
       <c r="I31" t="n">
-        <v>0.000128054758064263</v>
+        <v>0.0010083991066546</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1218,7 +1228,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1227,60 +1237,38 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>3.66240881979763e-11</v>
-      </c>
-      <c r="G32" t="n">
-        <v>8.062508206343759e-12</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.748824916236383e-10</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1.683907371141624e-10</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.103671384109167e-12</v>
-      </c>
-      <c r="K32" t="n">
-        <v>5.760775405349083e-10</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2050</v>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0.007194422490000695</v>
+      </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>0.0008048153837875063</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.0003912137147176</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.0060356504015384</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.0025226544953628</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.0003950537863859</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.0085810074458284</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1290,28 +1278,20 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>0.0024452817631911</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.0009171857712999</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.0291521602595318</v>
-      </c>
+        <v>1.83608376887917e-08</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.0074672623820571</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.0011690051194949</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.0415694018698083</v>
-      </c>
+        <v>4.084482658611099e-09</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1320,19 +1300,23 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.003340881264700904</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>0.01308643669280649</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6.640844061930469e-05</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>3.813628671025667e-05</v>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1340,50 +1324,206 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
-        <v>0.0141774429425305</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>0.000131868484186315</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>0.000128054758064263</v>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>2050</v>
       </c>
-      <c r="C37" t="n">
-        <v>0.00338334520507663</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.007194422490000695</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.0306047609000379</v>
-      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
+        <v>3.66240881979763e-11</v>
+      </c>
+      <c r="G37" t="n">
+        <v>8.062508206343759e-12</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.748824916236383e-10</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.683907371141624e-10</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.103671384109167e-12</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5.760775405349083e-10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Biogenic Liquids</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0.0008048153837875063</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0003912137147176</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0060356504015384</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0025226544953628</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.0003950537863859</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.0085810074458284</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fossil Liquids</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0.0024452817631911</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0009171857712999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0291521602595318</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.0074672623820571</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.0011690051194949</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.0415694018698083</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Biomass [Solid]</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>0.003340881264700904</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Fossil Rest</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Renewable Energy Carrier</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>0.0141774429425305</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Overall Demand</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.005709602905618179</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.01777328584704944</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.03462615247353184</v>
+      </c>
+      <c r="F43" t="n">
         <v>0.008584816107501003</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G43" t="n">
         <v>0.001308399494080008</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H43" t="n">
         <v>0.03518802507068995</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I43" t="n">
         <v>0.01116451128172241</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J43" t="n">
         <v>0.001564058907984471</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K43" t="n">
         <v>0.05015040989171424</v>
       </c>
     </row>

--- a/Outputs/PtX_demand_RO.xlsx
+++ b/Outputs/PtX_demand_RO.xlsx
@@ -503,11 +503,19 @@
       <c r="E2" t="n">
         <v>0.003837294723497144</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.01645711450450431</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0054385057909002</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0.0067536828970377</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0022912613703411</v>
+      </c>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -728,16 +736,18 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2030</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>0.005073237411109819</v>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.003278749924607429</v>
+        <v>0.02466053402023349</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -749,18 +759,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2030</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.005073237411109819</v>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.02466053402023349</v>
+        <v>0.003278749924607429</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -809,19 +817,19 @@
         <v>0.03451663800391957</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1583135045118776</v>
+        <v>0.1747706190163819</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001080196750447</v>
+        <v>0.0065187025413472</v>
       </c>
       <c r="H15" t="n">
         <v>0.03794892011421288</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1101174654360651</v>
+        <v>0.1168711483331028</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0017832717809829</v>
+        <v>0.004074533151324</v>
       </c>
       <c r="K15" t="n">
         <v>0.05287954780710969</v>
@@ -845,11 +853,19 @@
       <c r="E16" t="n">
         <v>0.003967993178665898</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.047145297467157</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0063825881748611</v>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.0221672230190457</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.002259716171466</v>
+      </c>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1074,16 +1090,18 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2040</v>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="n">
+        <v>0.002422206669268525</v>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>0.003322654056724997</v>
+        <v>0.01638187746695201</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1095,18 +1113,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2040</v>
       </c>
-      <c r="C27" t="n">
-        <v>0.002422206669268525</v>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>0.01638187746695201</v>
+        <v>0.003322654056724997</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1152,22 +1168,22 @@
         <v>0.01887017132778048</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03459377634697757</v>
+        <v>0.03459377634697758</v>
       </c>
       <c r="F29" t="n">
-        <v>0.05244919980495979</v>
+        <v>0.09959449727211678</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0012358269783492</v>
+        <v>0.0076184151532103</v>
       </c>
       <c r="H29" t="n">
         <v>0.03684057780043156</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0524058614584645</v>
+        <v>0.0745730844775102</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0016652804195508</v>
+        <v>0.0039249965910168</v>
       </c>
       <c r="K29" t="n">
         <v>0.05159914470403019</v>
@@ -1191,11 +1207,19 @@
       <c r="E30" t="n">
         <v>0.004021391573493941</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.05533447033966601</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0071676092172858</v>
+      </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.0321219410561958</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0023079024962823</v>
+      </c>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1432,7 +1456,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1440,9 +1464,7 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
-        <v>0.003340881264700904</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -1453,7 +1475,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1461,7 +1483,9 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>0.003340881264700904</v>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1506,22 +1530,22 @@
         <v>0.01777328584704944</v>
       </c>
       <c r="E43" t="n">
-        <v>0.03462615247353184</v>
+        <v>0.03462615247353183</v>
       </c>
       <c r="F43" t="n">
-        <v>0.008584816107501003</v>
+        <v>0.063919286447167</v>
       </c>
       <c r="G43" t="n">
-        <v>0.001308399494080008</v>
+        <v>0.008476008711365808</v>
       </c>
       <c r="H43" t="n">
         <v>0.03518802507068995</v>
       </c>
       <c r="I43" t="n">
-        <v>0.01116451128172241</v>
+        <v>0.04328645233791821</v>
       </c>
       <c r="J43" t="n">
-        <v>0.001564058907984471</v>
+        <v>0.003871961404266771</v>
       </c>
       <c r="K43" t="n">
         <v>0.05015040989171424</v>
